--- a/docs/algorithm-interview-learning/cards/algorithm-interview-lesson-01-constraint-driven-selection-technical-qa.xlsx
+++ b/docs/algorithm-interview-learning/cards/algorithm-interview-lesson-01-constraint-driven-selection-technical-qa.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -36,104 +36,129 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">算法题开场应按哪四类约束澄清，答案才会改变方案选择？</t>
+          <t xml:space="preserve">哪些约束会改变算法选择？</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：按数据特征、语义要求、访问模型和资源权限检查，并把每项约束映射到候选方案的开启或排除。
-• [T#B#数据特征]：规模、值域、重复性、已有有序性。
-• [T#B#语义要求]：稳定性、精确性、是否必须返回原始下标。
-• [T#B#访问模型]：输入表示、能否随机访问、能否多遍读取。
-• [T#B#资源权限]：能否修改输入、额外空间、内存上限。
-[T#B,!c47f17#边界]：只罗列关键词不够；必须说明每项约束会怎样改变候选方案。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：优先澄清会开启或排除候选方案的条件。
+• [T#B#数据]：规模、值域、重复性与已有顺序。
+• [T#B#语义]：稳定性、精确性、是否返回原下标。
+• [T#B#访问]：随机访问还是单遍流，能否多次读取。
+• [T#B#资源]：能否修改输入，以及额外空间上限。
+[T#B,!c47f17#边界]：每问一项，都要说明它会怎样改变方案；分类名称本身不是目的。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">数据—语义—访问—资源；约束必须改变方案</t>
+          <t xml:space="preserve">条件 → 候选方案</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lesson 01 学习记录｜E-01、E-05</t>
+          <t xml:space="preserve">算法 01 日志 · 约束澄清</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">非递减单遍流怎样用 O(1) 额外空间精确判重？</t>
+          <t xml:space="preserve">单遍流能直接复用数组双层枚举吗？</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：只保存前一个值；当前值与它相等时即可报告重复。
-• [T#B#证明]：若两个 x 之间有 y，非递减性给出 x ≤ y ≤ x，所以 y=x，重复值必连续。
-• [T#B#成本]：一次扫描是 O(n) 时间，只保存常数状态是 O(1) 额外空间。
-[T#B,!c47f17#边界]：任意顺序流不保证重复相邻，该方案不成立。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：先检查原基线需要的回看和随机访问是否仍然可用。
+• [T#B#原依赖]：数组双层枚举需要重复访问已见元素。
+• [T#B#访问变化]：单遍流消费过去的元素后，通常无法重新枚举。
+[T#B,!c47f17#边界]：若允许缓存或重放，要把对应空间和访问权限作为新条件重新分析。</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">非递减→相等值连续→只存前值；任意顺序失效</t>
+          <t xml:space="preserve">先可执行，再算复杂度</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lesson 01 学习记录｜E-05</t>
+          <t xml:space="preserve">算法 01 日志 · 数组到单遍流的转折</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">值域固定为 {0,1,2} 时，怎样在线性时间返回 Two Sum 的不同原下标？</t>
+          <t xml:space="preserve">非递减单遍流如何用常数空间判重？</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：扫描一次，对每个值最多保存两个不同原下标；扫描后只检查固定的六类无序值对。
-• [T#B#状态]：值域只有三个值，保存的下标总数有常数上限。
-• [T#B#候选]：检查 0+0、0+1、0+2、1+1、1+2、2+2。
-• [T#B#互异下标]：异值对各取一个下标；同值对必须已有两个不同下标。
-• [T#B#成本]：扫描是 O(n)，固定候选检查与额外状态均为 O(1)。
-[T#B,!c47f17#边界]：结论依赖值域固定为 {0,1,2}，且要求返回两个不同原下标。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：只保留前一个值，逐项比较相邻元素。
+• [T#B#依据]：两个相等的 x 之间若有 y，非递减性给出 x ≤ y ≤ x，因此重复值必相邻。
+• [T#B#成本]：扫描 O(n) 时间，保存常数个状态。
+[T#B,!c47f17#边界]：任意顺序流不保证重复相邻；空流和首元素处理是另行实现时要处理的边界。</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">每值至多两个下标；六类无序值对；同值需两个下标</t>
+          <t xml:space="preserve">顺序 → 重复相邻 → 前值比较</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lesson 01 学习记录｜E-03</t>
+          <t xml:space="preserve">算法 01 日志 · 非递减流迁移</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">一道算法题表现良好时，怎样给出不越界的面试评价？</t>
+          <t xml:space="preserve">固定值域 {0,1,2}，如何返回 Two Sum 原下标？</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：只评价本题中直接观察到的能力，并明确未观察范围。
-• [T#B#已观察]：约束澄清、正确基线、复杂度分析、优化探索和思路表达。
-• [T#B#未观察]：完整实现、调试、边界处理、系统设计和其他技术知识。
-[T#B,!c47f17#边界]：不能据一题局部表现直接推出整体岗位胜任或 Offer。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：每个值最多保存两个原下标，再检查固定的无序值对。
+• [T#B#状态]：一次扫描，为三个值各保留至多两个不同下标。
+• [T#B#枚举]：检查 0+0、0+1、0+2、1+1、1+2、2+2。
+• [T#B#互异]：异值各取一个下标；同值必须有两个不同下标。
+• [T#B#成本]：扫描 O(n)，固定大小的状态和候选检查为 O(1)。
+[T#B,!c47f17#边界]：依赖值域固定且要求不同原下标；不能直接推广到随输入增大的值域。</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">已观察—未观察—不作整体推断</t>
+          <t xml:space="preserve">有限状态；完整值对；不同下标</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lesson 01 学习记录｜E-04</t>
+          <t xml:space="preserve">算法 01 日志 · 固定值域纠错</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">一道题的好表现能支持多大范围的评价？</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：只陈述实际观察到的能力，同时列出未观察范围。
+• [T#B#已观察]：例如约束澄清、基线分析与思路表达。
+• [T#B#未观察]：没有实际展示的实现、调试或系统设计能力。
+[T#B,!c47f17#边界]：单题局部表现不足以直接推出整体岗位胜任。</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已观察 / 未观察</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">算法 01 日志 · 评价边界</t>
         </is>
       </c>
     </row>

--- a/docs/algorithm-interview-learning/cards/algorithm-interview-lesson-01-constraint-driven-selection-technical-qa.xlsx
+++ b/docs/algorithm-interview-learning/cards/algorithm-interview-lesson-01-constraint-driven-selection-technical-qa.xlsx
@@ -36,22 +36,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">哪些约束会改变算法选择？</t>
+          <t xml:space="preserve">算法面试中，拿到一个看似熟悉、但条件还未说清的问题时，应优先澄清哪些约束，并怎样说明这些约束会改变候选算法？</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：优先澄清会开启或排除候选方案的条件。
-• [T#B#数据]：规模、值域、重复性与已有顺序。
-• [T#B#语义]：稳定性、精确性、是否返回原下标。
-• [T#B#访问]：随机访问还是单遍流，能否多次读取。
-• [T#B#资源]：能否修改输入，以及额外空间上限。
-[T#B,!c47f17#边界]：每问一项，都要说明它会怎样改变方案；分类名称本身不是目的。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：围绕数据、输出语义、访问方式和资源限制澄清条件；每确认一项，都要指出它会让什么方案可用、不可用或需要重新分析。
+• [T#B#数据]：确认输入规模、值域、重复情况和已有顺序。规模影响计算成本能否接受；固定的小值域可能允许常数大小的状态；非递减顺序可能把判重转化为相邻比较。
+• [T#B#输出语义]：确认结果是否必须精确、是否要求稳定性，以及返回值还是原下标。例如 Two Sum 若要返回两个不同原下标，方案必须保存足够的下标信息，不能只判断某个和值可达。
+• [T#B#访问方式]：确认是可随机访问的数组还是单遍流，能否回看或重读。数组上的逐对枚举依赖重复访问；单遍流若不能重放，也没有缓存，就未必能执行原基线。
+• [T#B#资源限制]：确认能否修改输入、允许多少额外空间。只读限制会阻止直接重排原输入；常数额外空间会排除随输入规模增长的历史存储，但要继续检查固定值域等条件是否允许其他方案。
+[T#B,!c47f17#边界]：只追问会影响当前题目方案的条件，并把尚未确认的条件说成未知。背出分类名称，不能代替说明“这个条件为何影响算法”。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">条件 → 候选方案</t>
+          <t xml:space="preserve">明确条件；说明它为何开启或排除方案</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -63,20 +63,21 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">单遍流能直接复用数组双层枚举吗？</t>
+          <t xml:space="preserve">判断一批 ID 是否出现重复时，原方案在数组上逐对比较。若输入改成只能读一遍、不能回放且没有保存全部历史的 ID 流，为什么不能直接沿用这套双层枚举基线？</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：先检查原基线需要的回看和随机访问是否仍然可用。
-• [T#B#原依赖]：数组双层枚举需要重复访问已见元素。
-• [T#B#访问变化]：单遍流消费过去的元素后，通常无法重新枚举。
-[T#B,!c47f17#边界]：若允许缓存或重放，要把对应空间和访问权限作为新条件重新分析。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：原基线依赖能反复取得各个元素；单遍流改变了访问权限，所以必须先确认算法还能执行，再讨论它的时间复杂度。
+• [T#B#数组依赖]：在数组中，固定一个 ID 后可以访问其他位置进行比较，换下一个 ID 时还可以再次访问这些位置。逐对枚举的正确性和执行过程都依赖这种重复访问。
+• [T#B#条件变化]：单遍流的元素消费后，既不能回放，又没有完整历史缓存；当后面的 ID 到达时，先前的任意 ID 已经不一定可取。因此不能仅把原数组代码的输入类型换成流，就继续完成所有逐对比较。
+• [T#B#分析顺序]：应先明确允许保存什么状态、能否重读，以及流是否具有顺序保证，再判断可采用的判重方法。原数组算法的复杂度标签不能证明它在新访问模型中可执行。
+[T#B,!c47f17#边界]：如果允许缓存或重放，逐对比较的可行性可能改变，但必须重新计入缓存空间和读取权限。这里否定的是直接复用原基线，并未证明单遍流无法判重。</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">先可执行，再算复杂度</t>
+          <t xml:space="preserve">访问条件改变 → 重查基线可执行性 → 再算成本</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -88,20 +89,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">非递减单遍流如何用常数空间判重？</t>
+          <t xml:space="preserve">一条只能读取一遍的 ID 流保证按非递减顺序到达，目标是精确判断是否出现重复 ID。为什么只保留前一个值就足够，算法的时间和额外空间成本是什么？</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：只保留前一个值，逐项比较相邻元素。
-• [T#B#依据]：两个相等的 x 之间若有 y，非递减性给出 x ≤ y ≤ x，因此重复值必相邻。
-• [T#B#成本]：扫描 O(n) 时间，保存常数个状态。
-[T#B,!c47f17#边界]：任意顺序流不保证重复相邻；空流和首元素处理是另行实现时要处理的边界。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：非递减顺序保证重复值连续出现，因此逐项比较相邻 ID 即可；发现相等就能确认重复，不需要保存全部已见值。
+• [T#B#完整性依据]：设两个位置的 ID 都是 x，夹在它们之间的任一值为 y。非递减性同时限制 y 不小于前面的 x，也不大于后面的 x，所以 y 只能等于 x；只要出现重复，就一定存在一对相邻重复。
+[E##x\le y\le x\quad\Longrightarrow\quad y=x]
+• [T#B#扫描机制]：已有前一个值时，将新到达的 ID 与它比较；相等则报告重复，不等则用当前值更新前值并继续。相邻相等显然是真重复，而上面的顺序证明保证这个检查不会漏掉重复。
+• [T#B#成本来源]：设 n 为 ID 总数，最坏需要读完整条流，每次只做常数次比较和更新；保存的前值及必要状态数量不随 n 增长。
+[E##T(n)=O(n),\qquad S_{\mathrm{extra}}(n)=O(1)]
+[T#B,!c47f17#边界]：任意顺序流中的相同 ID 可能被其他值隔开，相邻比较就会漏检。本卡说明已确认的判重机制；空流、首元素初始化和哨兵冲突仍属于日志列出的后续实现边界。</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">顺序 → 重复相邻 → 前值比较</t>
+          <t xml:space="preserve">非递减保证重复相邻；前值比较即可检出</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -113,22 +117,24 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">固定值域 {0,1,2}，如何返回 Two Sum 原下标？</t>
+          <t xml:space="preserve">Two Sum 的输入是长度为 n 的只读数组，元素仅取固定的 0、1、2；给定 target，要返回一对不同的原下标，且只允许常数额外空间。怎样用一次扫描构造完整方案，并避免同一元素被用两次？</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：每个值最多保存两个原下标，再检查固定的无序值对。
-• [T#B#状态]：一次扫描，为三个值各保留至多两个不同下标。
-• [T#B#枚举]：检查 0+0、0+1、0+2、1+1、1+2、2+2。
-• [T#B#互异]：异值各取一个下标；同值必须有两个不同下标。
-• [T#B#成本]：扫描 O(n)，固定大小的状态和候选检查为 O(1)。
-[T#B,!c47f17#边界]：依赖值域固定且要求不同原下标；不能直接推广到随输入增大的值域。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：为三个可能的值各保存至多两个不同原下标，再检查所有无序值对。固定值域让状态数量保持常数，保存两个下标则能处理两个相同值配对的情况。
+• [T#B#保留状态]：扫描原数组时，按元素值记录下标；某个值已有两个下标后，无须继续保存它的更多出现位置。题目只要求返回一对解，所以每个值的前两个不同下标足以支持任意一次同值或异值配对。
+• [T#B#完整枚举]：扫描后检查下面六个无序值对，只考虑和值等于 target 的候选。它们覆盖三个值允许的全部配对，尤其不能漏掉零和二这一对。
+[E##(0,0),\ (0,1),\ (0,2),\ (1,1),\ (1,2),\ (2,2)]
+• [T#B#检查与返回]：异值配对要求两个值各有一个已记录下标；同值配对要求该值确实有两个不同下标。条件成立就返回对应原下标，不能把一个下标使用两次；若六对都不成立，就没有符合要求的解。
+• [T#B#成本与只读]：一次扫描的工作量随数组长度增长；最多保存六个下标，后续也只检查六个值对。全程读取原数组，不需要改变元素顺序。
+[E##T(n)=O(n),\qquad S_{\mathrm{extra}}(n)=O(1)]
+[T#B,!c47f17#边界]：常数空间结论依赖值域固定为这三个值，不能直接推广到值域随输入增长的情况。本方案返回一对解；它没有承诺保存或输出所有下标对。</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">有限状态；完整值对；不同下标</t>
+          <t xml:space="preserve">每值两下标；六种值对；异值各一、同值需二</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -140,20 +146,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">一道题的好表现能支持多大范围的评价？</t>
+          <t xml:space="preserve">一次算法面试练习中，候选人把某道题的约束、基线和优化思路解释清楚了，但尚未实际编写或调试代码。评价者能据此肯定哪些能力，怎样避免直接推断其整体岗位胜任？</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：只陈述实际观察到的能力，同时列出未观察范围。
-• [T#B#已观察]：例如约束澄清、基线分析与思路表达。
-• [T#B#未观察]：没有实际展示的实现、调试或系统设计能力。
-[T#B,!c47f17#边界]：单题局部表现不足以直接推出整体岗位胜任。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：评价范围应与实际观察到的表现一致：可以肯定本题中展示的分析与表达，同时明确实现、调试和其他岗位能力仍未得到观察。
+• [T#B#已观察]：具体陈述证据，例如能澄清影响算法的约束，说明基线的完整性和成本，并把候选方案与约束对应。这样评价有明确对象，别人也能检查依据。
+• [T#B#未观察]：没有实际编码或调试，就不能把思路清楚自动当成实现正确、调试熟练的证据；本题也没有展示系统设计能力。应将这些标为尚未观察，而不是直接判定优秀或不足。
+• [T#B#评价示例]：例如：“本题的约束澄清和方案解释已有清楚证据；代码实现、调试及系统设计尚未观察，暂不据此判断整体岗位胜任。”
+[T#B,!c47f17#边界]：单题的局部好表现可以支持局部判断，不能直接覆盖整个岗位所需能力。扩大结论范围，需要补充相应范围的实际证据。</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">已观察 / 未观察</t>
+          <t xml:space="preserve">证据覆盖到哪里，评价就说到哪里</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
